--- a/research/diwali-2026/diwali-2026-events-for-review.xlsx
+++ b/research/diwali-2026/diwali-2026-events-for-review.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -508,32 +508,32 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>all day</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Annual Diwali celebrations</t>
+          <t>Shiva Navgraha Pran Pratishtha Mahotsav</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>festival</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>An evening of music, dance, cultural performances, raffle prizes and a vegetarian meal, 7pm to 9pm. A free community event for the whole family.</t>
+          <t>Runs from 25 to 29 October at the mandir.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Read from the poster on their home page. It's tonight (23 Oct): add it today or skip it.</t>
+          <t>Home page lists it with no times.</t>
         </is>
       </c>
     </row>
@@ -560,12 +560,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Shiva Navgraha Pran Pratishtha Mahotsav</t>
+          <t>Karwa Chauth</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -583,11 +583,7 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Runs from 25 to 29 October at the mandir.</t>
-        </is>
-      </c>
+      <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>https://www.derbyhindutemple.com/</t>
@@ -612,22 +608,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>all day</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Karwa Chauth</t>
+          <t>Diwali: diya lighting, Laxmi puja and fireworks</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -635,7 +631,11 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Diya lighting from 4:30pm, Laxmi puja at 6:30pm and a fireworks display at 8pm. The mandir is open 9am to 9pm.</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>https://www.derbyhindutemple.com/</t>
@@ -643,7 +643,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Home page lists it with no times.</t>
+          <t>From the Diwali poster on their home page.</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Diwali: diya lighting, Laxmi puja and fireworks</t>
+          <t>Govardhan Puja</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Diya lighting from 4:30pm, Laxmi puja at 6:30pm and a fireworks display at 8pm. The mandir is open 9am to 9pm.</t>
+          <t>11am to 1pm, with prasad served from 1pm.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,39 +695,39 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>From the Diwali poster on their home page.</t>
+          <t>From the Govardhan Puja poster.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Hindu Temple Geeta Bhawan Derby</t>
+          <t>Sanatan Mandir Crawley (Apple Tree Centre)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Crawley</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Govardhan Puja</t>
+          <t>Karwa Chauth</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11am to 1pm, with prasad served from 1pm.</t>
+          <t>4pm to 5pm.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://www.derbyhindutemple.com/</t>
+          <t>https://www.crawleyhindu.com/events/view/175</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>From the Govardhan Puja poster.</t>
+          <t>From their Diwali &amp; New Year poster.</t>
         </is>
       </c>
     </row>
@@ -764,42 +764,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Karwa Chauth</t>
+          <t>Deepavali Utsav</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>festival</t>
+          <t>community</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4pm to 5pm.</t>
+          <t>Light refreshments at 5pm, a cultural show from 6pm to 8pm and speeches at 8pm, in the Dhamecha Suite. Tickets £5.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://www.crawleyhindu.com/events/view/175</t>
+          <t>https://www.crawleyhindu.com/events/view/176</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>From their Diwali &amp; New Year poster.</t>
+          <t>From the Deepavali Utsav poster.</t>
         </is>
       </c>
     </row>
@@ -816,44 +816,40 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Deepavali Utsav</t>
+          <t>Dhan Teras and Vagh Baras</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>festival</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Light refreshments at 5pm, a cultural show from 6pm to 8pm and speeches at 8pm, in the Dhamecha Suite. Tickets £5.</t>
+          <t>7pm to 9pm.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://www.crawleyhindu.com/events/view/176</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>From the Deepavali Utsav poster.</t>
-        </is>
-      </c>
+          <t>https://www.crawleyhindu.com/events/view/175</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -868,22 +864,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Dhan Teras and Vagh Baras</t>
+          <t>Diwali fireworks display</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -893,12 +889,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7pm to 9pm.</t>
+          <t>Fireworks at the Apple Tree Centre, 7:30pm to 8:30pm.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://www.crawleyhindu.com/events/view/175</t>
+          <t>https://www.crawleyhindu.com/events/view/177</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -926,12 +922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Diwali fireworks display</t>
+          <t>Diwali: Laxmi and Chopda pujan</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -941,12 +937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Fireworks at the Apple Tree Centre, 7:30pm to 8:30pm.</t>
+          <t>Chopda pujan from 8pm to 9:30pm. £51 per person for the pujan, first come first served.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://www.crawleyhindu.com/events/view/177</t>
+          <t>https://www.crawleyhindu.com/events/view/175</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -964,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Diwali: Laxmi and Chopda pujan</t>
+          <t>Nutan Varsh and Annakut darshan</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -989,7 +985,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Chopda pujan from 8pm to 9:30pm. £51 per person for the pujan, first come first served.</t>
+          <t>Nitya shringar aarti at 10am; Rajbhog, Annakut darshan and samuha aarti at 1pm; Nutan Varsh maha aarti at 7pm; Annakut mahaprasad at 7:30pm.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1012,22 +1008,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Nutan Varsh and Annakut darshan</t>
+          <t>Jalaram Jayanti</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1037,7 +1033,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Nitya shringar aarti at 10am; Rajbhog, Annakut darshan and samuha aarti at 1pm; Nutan Varsh maha aarti at 7pm; Annakut mahaprasad at 7:30pm.</t>
+          <t>1pm to 5pm, with prasad at 5pm.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1050,32 +1046,32 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Sanatan Mandir Crawley (Apple Tree Centre)</t>
+          <t>Shree Swaminarayan Temple Cardiff</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Crawley</t>
+          <t>Cardiff</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Jalaram Jayanti</t>
+          <t>Dhanteras: Diwali parade</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,15 +1081,19 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1pm to 5pm, with prasad at 5pm.</t>
+          <t>Sandhya aarti at 6pm, the Diwali parade at 6:30pm and shayan aarti at 7:30pm.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://www.crawleyhindu.com/events/view/175</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr"/>
+          <t>https://swaminarayan.wales/general-events/diwali-celebrations-2026</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Their page's heading gives Sat 8 and Sun 9 November by mistake; the day-by-day timetable on the same page says Fri 6 to Mon 9, which is what's used here.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1108,22 +1108,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Dhanteras: Diwali parade</t>
+          <t>Kali Chaudas: Hanuman poojan</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Sandhya aarti at 6pm, the Diwali parade at 6:30pm and shayan aarti at 7:30pm.</t>
+          <t>Family poojans at 9am and 10am, katha at 4:30pm, sandhya aarti at 5pm, then Hanuman poojan, chalisa and aarti at 5:30pm.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Kali Chaudas: Hanuman poojan</t>
+          <t>Diwali: Chopda poojan and street food festival</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Family poojans at 9am and 10am, katha at 4:30pm, sandhya aarti at 5pm, then Hanuman poojan, chalisa and aarti at 5:30pm.</t>
+          <t>Katha at 4pm, Chopda poojan at 4:30pm, sandhya aarti at 5pm and a street food festival from 5:30pm to 8pm.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1212,22 +1212,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Diwali: Chopda poojan and street food festival</t>
+          <t>Ankoot Utsav and Hindu New Year</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Katha at 4pm, Chopda poojan at 4:30pm, sandhya aarti at 5pm and a street food festival from 5:30pm to 8pm.</t>
+          <t>Aarti 7:30am, bhajans 9am, katha and greetings 9:30am, Ankoot aarti 11am, mahaprasad 11:30am, raas 5pm, sandhya aarti 5:30pm and Ankoot prasad 6:30pm.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1254,32 +1254,32 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Shree Swaminarayan Temple Cardiff</t>
+          <t>Shree Swaminarayan Temple Stanmore</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Cardiff</t>
+          <t>Stanmore</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Ankoot Utsav and Hindu New Year</t>
+          <t>Sharad Purnima</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1289,19 +1289,15 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Aarti 7:30am, bhajans 9am, katha and greetings 9:30am, Ankoot aarti 11am, mahaprasad 11:30am, raas 5pm, sandhya aarti 5:30pm and Ankoot prasad 6:30pm.</t>
+          <t>Aarti, katha, kirtan and dhun from 5:30pm, then Raas Leela from 6:30pm, in the Gents &amp; Ladies Mandir.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://swaminarayan.wales/general-events/diwali-celebrations-2026</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>Their page's heading gives Sat 8 and Sun 9 November by mistake; the day-by-day timetable on the same page says Fri 6 to Mon 9, which is what's used here.</t>
-        </is>
-      </c>
+          <t>https://stanmoretemple.com/events/sharad-purnima-2026</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1316,22 +1312,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Sharad Purnima</t>
+          <t>Kali Chaudas: Hanuman pujan</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1341,12 +1337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Aarti, katha, kirtan and dhun from 5:30pm, then Raas Leela from 6:30pm, in the Gents &amp; Ladies Mandir.</t>
+          <t>Hanuman Chalisa 4pm to 5:30pm, Hanuman pujan at 6pm, Hanuman Chalisa and Bajrang Baan at 7pm, and maha aarti at 8pm.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://stanmoretemple.com/events/sharad-purnima-2026</t>
+          <t>https://stanmoretemple.com/events/diwali-2026</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1364,22 +1360,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Kali Chaudas: Hanuman pujan</t>
+          <t>Diwali: Laxmi and Chopda pujan, and fireworks</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1389,7 +1385,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Hanuman Chalisa 4pm to 5:30pm, Hanuman pujan at 6pm, Hanuman Chalisa and Bajrang Baan at 7pm, and maha aarti at 8pm.</t>
+          <t>Laxmi and Chopda pujan at 4:30pm (register first, then bring your own chopda and red pen), sandhya aarti at 5:30pm, and fireworks night on the event field from 6pm, with fireworks at 8pm. Free entry and parking.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1412,22 +1408,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Diwali: Laxmi and Chopda pujan, and fireworks</t>
+          <t>Nutan Varsh: Annakut darshan</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1437,7 +1433,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Laxmi and Chopda pujan at 4:30pm (register first, then bring your own chopda and red pen), sandhya aarti at 5:30pm, and fireworks night on the event field from 6pm, with fireworks at 8pm. Free entry and parking.</t>
+          <t>Annakut darshan from 7am with aarti every hour, and sandhya aarti with the last Annakut darshan at 6:30pm.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1450,32 +1446,32 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Shree Swaminarayan Temple Stanmore</t>
+          <t>Shri Sanatan Hindu Mandir (Shri Vallabh Nidhi UK)</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Stanmore</t>
+          <t>Wembley</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Nutan Varsh: Annakut darshan</t>
+          <t>Kaali Chaudash: Hanuman Chalisa</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1485,15 +1481,19 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Annakut darshan from 7am with aarti every hour, and sandhya aarti with the last Annakut darshan at 6:30pm.</t>
+          <t>Hanuman Chalisa from 10am to 1pm.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://stanmoretemple.com/events/diwali-2026</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr"/>
+          <t>https://svnuk.com/singlee/diwali-nutan-varsh-2026/</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>From the Diwali &amp; Nutan Varsh poster on this page.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1508,22 +1508,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Kaali Chaudash: Hanuman Chalisa</t>
+          <t>Diwali: Chopda and Laxmi pujan</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Hanuman Chalisa from 10am to 1pm.</t>
+          <t>Chopda and Laxmi pujan at 11am. Anyone can take part by donating £51 per person.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1560,22 +1560,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Diwali: Chopda and Laxmi pujan</t>
+          <t>Nutan Varsh and Annakoot darshan</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Chopda and Laxmi pujan at 11am. Anyone can take part by donating £51 per person.</t>
+          <t>Annakoot darshan from 7am to 7pm, with the Nutan Varsh maha aarti at 12 noon and aartis through the day.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1602,52 +1602,52 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Shri Sanatan Hindu Mandir (Shri Vallabh Nidhi UK)</t>
+          <t>Shree Krishna Mandir West Bromwich</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Wembley</t>
+          <t>West Bromwich</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Nutan Varsh and Annakoot darshan</t>
+          <t>Youth Club Diwali party</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>festival</t>
+          <t>youth</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Annakoot darshan from 7am to 7pm, with the Nutan Varsh maha aarti at 12 noon and aartis through the day.</t>
+          <t>2pm to 5pm: arts and crafts, carrom, Diwali games, a rangoli competition, light-up sparklers and a buffet. £2 per person, under-5s free. Please let the mandir know you're coming.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://svnuk.com/singlee/diwali-nutan-varsh-2026/</t>
+          <t>https://www.shreekrishnamandir.org/</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>From the Diwali &amp; Nutan Varsh poster on this page.</t>
+          <t>From the Youth Club poster. The poster gives a named person's phone number for RSVPs; left out on purpose.</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1679,17 +1679,17 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Youth Club Diwali party</t>
+          <t>Diwali celebrations</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>youth</t>
+          <t>festival</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2pm to 5pm: arts and crafts, carrom, Diwali games, a rangoli competition, light-up sparklers and a buffet. £2 per person, under-5s free. Please let the mandir know you're coming.</t>
+          <t>From 2pm: chai nasto, festive games, light a diya, fireworks and aarti. Everyone welcome, free entry.</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1699,39 +1699,39 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>From the Youth Club poster. The poster gives a named person's phone number for RSVPs; left out on purpose.</t>
+          <t>From the Diwali Celebrations poster.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Shree Krishna Mandir West Bromwich</t>
+          <t>The Hindu Temple Bristol</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>West Bromwich</t>
+          <t>Bristol</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Diwali celebrations</t>
+          <t>Karwa Chauth</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1741,19 +1741,15 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>From 2pm: chai nasto, festive games, light a diya, fireworks and aarti. Everyone welcome, free entry.</t>
+          <t>4pm to 7:30pm.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://www.shreekrishnamandir.org/</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>From the Diwali Celebrations poster.</t>
-        </is>
-      </c>
+          <t>https://hindutemplebristol.co.uk/mandir-events/</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1768,22 +1764,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>all day</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Sharad Purnima Garba</t>
+          <t>Kali Chaudas: 25 Hanuman Chalisa</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1793,7 +1789,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Garba in the mandir from 7:30pm.</t>
+          <t>25 Hanuman Chalisa recitations. Time to be confirmed.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1801,11 +1797,7 @@
           <t>https://hindutemplebristol.co.uk/mandir-events/</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>It's tonight (23 Oct): add it today or skip it.</t>
-        </is>
-      </c>
+      <c r="J27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1820,22 +1812,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Karwa Chauth</t>
+          <t>Diwali: Chopda pujan</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1845,7 +1837,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4pm to 7:30pm.</t>
+          <t>Chopda pujan at 8pm.</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1868,22 +1860,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>all day</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Kali Chaudas: 25 Hanuman Chalisa</t>
+          <t>Annakut</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1893,7 +1885,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25 Hanuman Chalisa recitations. Time to be confirmed.</t>
+          <t>Annakut aarti at 12:30pm and evening aarti at 8pm.</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1901,17 +1893,21 @@
           <t>https://hindutemplebristol.co.uk/mandir-events/</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Bristol holds Annakut on Tuesday 10 November (their calendar gives Bestu Varsh as the 10th).</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>The Hindu Temple Bristol</t>
+          <t>Hindu Temple Cultural and Community Centre</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Bristol</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1926,12 +1922,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Diwali: Chopda pujan</t>
+          <t>Diwali celebration</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1941,12 +1937,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Chopda pujan at 8pm.</t>
+          <t>Traditional prayers, aarti and cultural performances from 6pm.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://hindutemplebristol.co.uk/mandir-events/</t>
+          <t>https://www.hindutemple.org.uk/events-bookings/2026-diwali-8th-november-2026-6pm</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -1954,32 +1950,32 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>The Hindu Temple Bristol</t>
+          <t>Bhaktivedanta Manor (ISKCON)</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Bristol</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>all day</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Annakut</t>
+          <t>Diwali festival</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1989,49 +1985,45 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Annakut aarti at 12:30pm and evening aarti at 8pm.</t>
+          <t>Darshan, drama, dances, children's activities and prasad. Free, but you need a ticket: tickets are released on Sunday 1 November at 12 noon. There are no fireworks this year.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>https://hindutemplebristol.co.uk/mandir-events/</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>Bristol holds Annakut on Tuesday 10 November (their calendar gives Bestu Varsh as the 10th).</t>
-        </is>
-      </c>
+          <t>https://www.krishnatemple.com/event/diwali-festival/</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Hindu Temple Cultural and Community Centre</t>
+          <t>Bhaktivedanta Manor (ISKCON)</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>all day</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Diwali celebration</t>
+          <t>Annakuta and Govardhan puja</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2041,12 +2033,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Traditional prayers, aarti and cultural performances from 6pm.</t>
+          <t>No ticket needed.</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://www.hindutemple.org.uk/events-bookings/2026-diwali-8th-november-2026-6pm</t>
+          <t>https://www.krishnatemple.com/event/annakuta-govardhana-puja/</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -2054,17 +2046,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Bhaktivedanta Manor (ISKCON)</t>
+          <t>Gujarat Hindu Society and Community Centre</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Preston</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2079,7 +2071,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Diwali festival</t>
+          <t>Sharad Purnima</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2087,62 +2079,62 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Darshan, drama, dances, children's activities and prasad. Free, but you need a ticket: tickets are released on Sunday 1 November at 12 noon. There are no fireworks this year.</t>
-        </is>
-      </c>
+      <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://www.krishnatemple.com/event/diwali-festival/</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr"/>
+          <t>https://www.ghspreston.co.uk/ghs-events-calendar/</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>From their 2026 festivals and programmes calendar (no times given).</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Bhaktivedanta Manor (ISKCON)</t>
+          <t>Gujarat Hindu Society and Community Centre</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Preston</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>all day</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Annakuta and Govardhan puja</t>
+          <t>Children's Diwali party</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>festival</t>
+          <t>youth</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>No ticket needed.</t>
+          <t>Bring children at 3pm and collect them at 6pm. Volunteers are welcome to help with games.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://www.krishnatemple.com/event/annakuta-govardhana-puja/</t>
+          <t>https://www.ghspreston.co.uk/calendar/childrens-diwali-party-sat-31st-oct-2026/</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
@@ -2160,7 +2152,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2170,30 +2162,30 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>all day</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Sharad Purnima</t>
+          <t>Bhajan Bhojan</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>festival</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
+          <t>bhajan</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Morning aarti at 9:30am, children's bhajans from 11am to 12:30pm, and bhajans and bhojan through the day until 4pm. Everyone welcome.</t>
+        </is>
+      </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>https://www.ghspreston.co.uk/ghs-events-calendar/</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>From their 2026 festivals and programmes calendar (no times given).</t>
-        </is>
-      </c>
+          <t>https://www.ghspreston.co.uk/calendar/bhajan-bhojan-sun-1st-nov-2026/</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2208,12 +2200,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2223,7 +2215,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Children's Diwali party</t>
+          <t>Rangoli competition</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -2233,12 +2225,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Bring children at 3pm and collect them at 6pm. Volunteers are welcome to help with games.</t>
+          <t>For ages 4 to 15, 3pm to 5pm. 50p per entry; collect an entry form from the office.</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://www.ghspreston.co.uk/calendar/childrens-diwali-party-sat-31st-oct-2026/</t>
+          <t>https://www.ghspreston.co.uk/calendar/rangoli-competition-sun-1st-nov-2026/</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -2266,27 +2258,27 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Bhajan Bhojan</t>
+          <t>Aarti thali decoration competition</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>bhajan</t>
+          <t>community</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Morning aarti at 9:30am, children's bhajans from 11am to 12:30pm, and bhajans and bhojan through the day until 4pm. Everyone welcome.</t>
+          <t>Decorate a 12-inch thali at home and bring it to the mandir by 2:30pm; judging at 4pm.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>https://www.ghspreston.co.uk/calendar/bhajan-bhojan-sun-1st-nov-2026/</t>
+          <t>https://www.ghspreston.co.uk/calendar/aarti-thali-decoration-competition-sun-1st-nov-2026/</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
@@ -2304,7 +2296,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2314,30 +2306,30 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>all day</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Rangoli competition</t>
+          <t>Diwali and fireworks</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>youth</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>For ages 4 to 15, 3pm to 5pm. 50p per entry; collect an entry form from the office.</t>
-        </is>
-      </c>
+          <t>festival</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://www.ghspreston.co.uk/calendar/rangoli-competition-sun-1st-nov-2026/</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr"/>
+          <t>https://www.ghspreston.co.uk/ghs-events-calendar/</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>From their 2026 festivals and programmes calendar (no times given).</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2352,55 +2344,55 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>all day</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Aarti thali decoration competition</t>
+          <t>New Year and Annakut</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>community</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Decorate a 12-inch thali at home and bring it to the mandir by 2:30pm; judging at 4pm.</t>
-        </is>
-      </c>
+          <t>festival</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://www.ghspreston.co.uk/calendar/aarti-thali-decoration-competition-sun-1st-nov-2026/</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr"/>
+          <t>https://www.ghspreston.co.uk/ghs-events-calendar/</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>From their 2026 festivals and programmes calendar (no times given).</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Hindu Society and Community Centre</t>
+          <t>Shree Hindu Temple and Community Centre</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Preston</t>
+          <t>Leicester</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2410,12 +2402,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>all day</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Diwali and fireworks</t>
+          <t>Sharad Purnima</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -2423,37 +2415,37 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>From 7:30pm until late. Tickets £5 from the mandir.</t>
+        </is>
+      </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://www.ghspreston.co.uk/ghs-events-calendar/</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>From their 2026 festivals and programmes calendar (no times given).</t>
-        </is>
-      </c>
+          <t>https://www.shreehindutemple.net/</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Hindu Society and Community Centre</t>
+          <t>Shree Hindu Temple and Community Centre</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Preston</t>
+          <t>Leicester</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2463,7 +2455,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>New Year and Annakut</t>
+          <t>Diwali: Chopda pujan</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -2471,15 +2463,19 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Chopda pujan in the mandir. Times to be confirmed.</t>
+        </is>
+      </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://www.ghspreston.co.uk/ghs-events-calendar/</t>
+          <t>https://www.shreehindutemple.net/hinduism/festivals-list-2026/</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>From their 2026 festivals and programmes calendar (no times given).</t>
+          <t>From their 2026 festivals list.</t>
         </is>
       </c>
     </row>
@@ -2496,22 +2492,22 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>all day</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Sharad Purnima</t>
+          <t>New Year and Annakut darshan</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -2521,30 +2517,34 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>From 7:30pm until late. Tickets £5 from the mandir.</t>
+          <t>Vikram Samvat 2083. Times to be confirmed.</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://www.shreehindutemple.net/</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr"/>
+          <t>https://www.shreehindutemple.net/hinduism/festivals-list-2026/</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>From their 2026 festivals list.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Shree Hindu Temple and Community Centre</t>
+          <t>Shree Jalaram Mandir Greenford</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Leicester</t>
+          <t>Greenford</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Diwali: Chopda pujan</t>
+          <t>Sharad Purnima</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2567,41 +2567,37 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Chopda pujan in the mandir. Times to be confirmed.</t>
-        </is>
-      </c>
+      <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>https://www.shreehindutemple.net/hinduism/festivals-list-2026/</t>
+          <t>https://jalarammandir.co.uk/events/</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>From their 2026 festivals list.</t>
+          <t>From their events list (no times given).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Shree Hindu Temple and Community Centre</t>
+          <t>Shree Jalaram Mandir Greenford</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Leicester</t>
+          <t>Greenford</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2611,7 +2607,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>New Year and Annakut darshan</t>
+          <t>Diwali and Chopda pujan</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2619,19 +2615,15 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Vikram Samvat 2083. Times to be confirmed.</t>
-        </is>
-      </c>
+      <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://www.shreehindutemple.net/hinduism/festivals-list-2026/</t>
+          <t>https://jalarammandir.co.uk/events/</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>From their 2026 festivals list.</t>
+          <t>From their events list (no times given).</t>
         </is>
       </c>
     </row>
@@ -2648,12 +2640,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2663,7 +2655,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Sharad Purnima</t>
+          <t>Nutan Varsh and Annakut darshan</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2696,12 +2688,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2711,7 +2703,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Diwali and Chopda pujan</t>
+          <t>227th Jalaram Jayanti celebration</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -2734,32 +2726,32 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Shree Jalaram Mandir Greenford</t>
+          <t>Shree Kutch Satsang Swaminarayan Temple</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Greenford</t>
+          <t>Kenton</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>all day</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Nutan Varsh and Annakut darshan</t>
+          <t>Sharad Poonam</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -2767,37 +2759,37 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Aarti, thaal, chesta and katha from 4:30pm to 6:15pm, raas from 6:15pm to 7pm, then the Sharad Poonam aarti with dudhpaak, puri and marcha prasad for all.</t>
+        </is>
+      </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>https://jalarammandir.co.uk/events/</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>From their events list (no times given).</t>
-        </is>
-      </c>
+          <t>https://sksst.org/</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Shree Jalaram Mandir Greenford</t>
+          <t>Shree Kutch Satsang Swaminarayan Temple</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Greenford</t>
+          <t>Kenton</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2807,7 +2799,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>227th Jalaram Jayanti celebration</t>
+          <t>Kali Chaudash: Hanuman pujan</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2815,15 +2807,19 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Timings to be confirmed.</t>
+        </is>
+      </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>https://jalarammandir.co.uk/events/</t>
+          <t>https://sksst.org/</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>From their events list (no times given).</t>
+          <t>The mandir says timings will be shared nearer the time.</t>
         </is>
       </c>
     </row>
@@ -2840,7 +2836,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2850,12 +2846,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>all day</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Sharad Poonam</t>
+          <t>Diwali: Laxmi and Chopda pujan</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -2865,7 +2861,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Aarti, thaal, chesta and katha from 4:30pm to 6:15pm, raas from 6:15pm to 7pm, then the Sharad Poonam aarti with dudhpaak, puri and marcha prasad for all.</t>
+          <t>Timings to be confirmed.</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2873,7 +2869,11 @@
           <t>https://sksst.org/</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>The mandir says timings will be shared nearer the time.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Kali Chaudash: Hanuman pujan</t>
+          <t>Annakutotsav and Nutan Varsh</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Timings to be confirmed.</t>
+          <t>Govardhan pujan and the new year. Timings to be confirmed.</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2930,17 +2930,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Shree Kutch Satsang Swaminarayan Temple</t>
+          <t>Shree Swaminarayan Mandir Oldham</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Kenton</t>
+          <t>Oldham</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>all day</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Diwali: Laxmi and Chopda pujan</t>
+          <t>Sharad Poonam</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -2965,49 +2965,45 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Timings to be confirmed.</t>
+          <t>Raas followed by dudhpak prasad, from 6:30pm.</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>https://sksst.org/</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>The mandir says timings will be shared nearer the time.</t>
-        </is>
-      </c>
+          <t>https://oldhammandir.faith/</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Shree Kutch Satsang Swaminarayan Temple</t>
+          <t>Shri Venkateswara (Balaji) Temple</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Kenton</t>
+          <t>Tividale</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>all day</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Annakutotsav and Nutan Varsh</t>
+          <t>Festival of Lights: peace walk and fireworks</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -3017,86 +3013,78 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Govardhan pujan and the new year. Timings to be confirmed.</t>
+          <t>A peace walk from the Balaji Temple at 5:30pm and a fireworks display at 7pm.</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://sksst.org/</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>The mandir says timings will be shared nearer the time.</t>
-        </is>
-      </c>
+          <t>https://www.venkateswara.org.uk/religious-events/festival-of-lights-to-celebrate-deepawali-2026</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Shree Swaminarayan Mandir Oldham</t>
+          <t>Shri Venkateswara (Balaji) Temple</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Oldham</t>
+          <t>Tividale</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Ramayan: the divine Diwali story</t>
+          <t>Deepawali Samuha Dhanalakshmi pooja</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>youth</t>
+          <t>festival</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>The Bal Mandal (children's group) present the Ramayan on stage, from 7pm, followed by light nasto.</t>
+          <t>Group Dhanalakshmi pooja at 6:30pm.</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>https://oldhammandir.faith/</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>From the poster on their home page.</t>
-        </is>
-      </c>
+          <t>https://www.venkateswara.org.uk/religious-events/deepawali-samuha-dhanalakshmi-pooja-2026</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Shree Swaminarayan Mandir Oldham</t>
+          <t>London Sri Mahalakshmi Temple</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Oldham</t>
+          <t>East Ham</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3106,12 +3094,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Sharad Poonam</t>
+          <t>Deepavali: Kedara Gowri pooja</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -3121,12 +3109,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Raas followed by dudhpak prasad, from 6:30pm.</t>
+          <t>Kedara Gowri pooja at 3pm and 6pm.</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://oldhammandir.faith/</t>
+          <t>https://www.srimahalakshmitemple.net/UpcomingEvents.cshtml</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -3134,12 +3122,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Shri Venkateswara (Balaji) Temple</t>
+          <t>Sri Raja Rajeswary Amman Temple</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Tividale</t>
+          <t>Stoneleigh</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3154,12 +3142,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>all day</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Festival of Lights: peace walk and fireworks</t>
+          <t>Deepavali and Kethara Gowri Viratham</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -3167,14 +3155,10 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>A peace walk from the Balaji Temple at 5:30pm and a fireworks display at 7pm.</t>
-        </is>
-      </c>
+      <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>https://www.venkateswara.org.uk/religious-events/festival-of-lights-to-celebrate-deepawali-2026</t>
+          <t>https://srirajarajeswary.org.uk/event/</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
@@ -3182,17 +3166,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Shri Venkateswara (Balaji) Temple</t>
+          <t>ISKCON London (Radha Krishna Temple Soho)</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Tividale</t>
+          <t>Soho</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3202,12 +3186,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Deepawali Samuha Dhanalakshmi pooja</t>
+          <t>Sharad Purnima</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -3217,12 +3201,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Group Dhanalakshmi pooja at 6:30pm.</t>
+          <t>6pm to 9:30pm.</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://www.venkateswara.org.uk/religious-events/deepawali-samuha-dhanalakshmi-pooja-2026</t>
+          <t>https://iskcon.london/</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
@@ -3230,12 +3214,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>London Sri Mahalakshmi Temple</t>
+          <t>ISKCON Leicester</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>East Ham</t>
+          <t>Leicester</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3250,12 +3234,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>all day</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Deepavali: Kedara Gowri pooja</t>
+          <t>Dipavali</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -3263,37 +3247,37 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>Kedara Gowri pooja at 3pm and 6pm.</t>
-        </is>
-      </c>
+      <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>https://www.srimahalakshmitemple.net/UpcomingEvents.cshtml</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr"/>
+          <t>https://iskconleicester.org/</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>From the mandir's festival calendar (an observance list with no times), so check they're holding a programme.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Sri Raja Rajeswary Amman Temple</t>
+          <t>ISKCON Leicester</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Stoneleigh</t>
+          <t>Leicester</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3303,7 +3287,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Deepavali and Kethara Gowri Viratham</t>
+          <t>Govardhan puja</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -3314,202 +3298,62 @@
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://srirajarajeswary.org.uk/event/</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr"/>
+          <t>https://iskconleicester.org/</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>From the mandir's festival calendar (an observance list with no times), so check they're holding a programme.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>ISKCON London (Radha Krishna Temple Soho)</t>
+          <t>Wellingborough Hindu Mandir (WDHA)</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Soho</t>
+          <t>Wellingborough</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Sharad Purnima</t>
+          <t>Wellingborough Festival of Lights</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>festival</t>
+          <t>community</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>6pm to 9:30pm.</t>
+          <t>The town's Festival of Lights returns, 11am to 9pm, with workshops, performances and more across Wellingborough. See the WDHA page for where things are.</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>https://iskcon.london/</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>ISKCON Leicester</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Leicester</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-08</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>all day</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>Dipavali</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>festival</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>https://iskconleicester.org/</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>From the mandir's festival calendar (an observance list with no times), so check they're holding a programme.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>ISKCON Leicester</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Leicester</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>all day</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>Govardhan puja</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>festival</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>https://iskconleicester.org/</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>From the mandir's festival calendar (an observance list with no times), so check they're holding a programme.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Wellingborough Hindu Mandir (WDHA)</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Wellingborough</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>Wellingborough Festival of Lights</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>community</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>The town's Festival of Lights returns, 11am to 9pm, with workshops, performances and more across Wellingborough. See the WDHA page for where things are.</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
           <t>https://wdha.co.uk/calendar/wellingborough-festival-of-lights-2026/</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>A town-wide event the WDHA is part of, not only at the mandir; their page doesn't name one venue.</t>
         </is>
@@ -3526,7 +3370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3589,17 +3433,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Annual Diwali celebrations</t>
+          <t>Shiva Navgraha Pran Pratishtha Mahotsav</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3609,15 +3448,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>festival</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>An evening of music, dance, cultural performances, raffle prizes and a vegetarian meal, 7pm to 9pm. A free community event for the whole family.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Runs from 25 to 29 October at the mandir.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3627,13 +3465,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Shiva Navgraha Pran Pratishtha Mahotsav</t>
+          <t>Karwa Chauth</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3646,12 +3483,6 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Runs from 25 to 29 October at the mandir.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3661,13 +3492,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>2026-11-08</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Karwa Chauth</t>
+          <t>Diwali: diya lighting, Laxmi puja and fireworks</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3680,8 +3515,11 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Diya lighting from 4:30pm, Laxmi puja at 6:30pm and a fireworks display at 8pm. The mandir is open 9am to 9pm.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3691,17 +3529,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Diwali: diya lighting, Laxmi puja and fireworks</t>
+          <t>Govardhan Puja</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3716,35 +3554,34 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Diya lighting from 4:30pm, Laxmi puja at 6:30pm and a fireworks display at 8pm. The mandir is open 9am to 9pm.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>11am to 1pm, with prasad served from 1pm.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hindu-temple-geeta-bhawan-derby</t>
+          <t>sanatan-mandir-crawley-apple-tree-centre</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Govardhan Puja</t>
+          <t>Karwa Chauth</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.derbyhindutemple.com/</t>
+          <t>https://www.crawleyhindu.com/events/view/175</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3754,10 +3591,9 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>11am to 1pm, with prasad served from 1pm.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>4pm to 5pm.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3767,35 +3603,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Karwa Chauth</t>
+          <t>Deepavali Utsav</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.crawleyhindu.com/events/view/175</t>
+          <t>https://www.crawleyhindu.com/events/view/176</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>festival</t>
+          <t>community</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4pm to 5pm.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Light refreshments at 5pm, a cultural show from 6pm to 8pm and speeches at 8pm, in the Dhamecha Suite. Tickets £5.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3805,35 +3640,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Deepavali Utsav</t>
+          <t>Dhan Teras and Vagh Baras</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.crawleyhindu.com/events/view/176</t>
+          <t>https://www.crawleyhindu.com/events/view/175</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>festival</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Light refreshments at 5pm, a cultural show from 6pm to 8pm and speeches at 8pm, in the Dhamecha Suite. Tickets £5.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>7pm to 9pm.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3843,22 +3677,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Dhan Teras and Vagh Baras</t>
+          <t>Diwali fireworks display</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.crawleyhindu.com/events/view/175</t>
+          <t>https://www.crawleyhindu.com/events/view/177</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3868,10 +3702,9 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7pm to 9pm.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Fireworks at the Apple Tree Centre, 7:30pm to 8:30pm.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3886,17 +3719,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Diwali fireworks display</t>
+          <t>Diwali: Laxmi and Chopda pujan</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.crawleyhindu.com/events/view/177</t>
+          <t>https://www.crawleyhindu.com/events/view/175</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3906,10 +3739,9 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fireworks at the Apple Tree Centre, 7:30pm to 8:30pm.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Chopda pujan from 8pm to 9:30pm. £51 per person for the pujan, first come first served.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3919,17 +3751,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Diwali: Laxmi and Chopda pujan</t>
+          <t>Nutan Varsh and Annakut darshan</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3944,10 +3776,9 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chopda pujan from 8pm to 9:30pm. £51 per person for the pujan, first come first served.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Nitya shringar aarti at 10am; Rajbhog, Annakut darshan and samuha aarti at 1pm; Nutan Varsh maha aarti at 7pm; Annakut mahaprasad at 7:30pm.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3957,17 +3788,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nutan Varsh and Annakut darshan</t>
+          <t>Jalaram Jayanti</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3982,35 +3813,34 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nitya shringar aarti at 10am; Rajbhog, Annakut darshan and samuha aarti at 1pm; Nutan Varsh maha aarti at 7pm; Annakut mahaprasad at 7:30pm.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>1pm to 5pm, with prasad at 5pm.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sanatan-mandir-crawley-apple-tree-centre</t>
+          <t>shree-swaminarayan-temple-cardiff</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Jalaram Jayanti</t>
+          <t>Dhanteras: Diwali parade</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.crawleyhindu.com/events/view/175</t>
+          <t>https://swaminarayan.wales/general-events/diwali-celebrations-2026</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -4020,10 +3850,9 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1pm to 5pm, with prasad at 5pm.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Sandhya aarti at 6pm, the Diwali parade at 6:30pm and shayan aarti at 7:30pm.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4033,17 +3862,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Dhanteras: Diwali parade</t>
+          <t>Kali Chaudas: Hanuman poojan</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -4058,10 +3887,9 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sandhya aarti at 6pm, the Diwali parade at 6:30pm and shayan aarti at 7:30pm.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Family poojans at 9am and 10am, katha at 4:30pm, sandhya aarti at 5pm, then Hanuman poojan, chalisa and aarti at 5:30pm.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4071,17 +3899,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Kali Chaudas: Hanuman poojan</t>
+          <t>Diwali: Chopda poojan and street food festival</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4096,10 +3924,9 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Family poojans at 9am and 10am, katha at 4:30pm, sandhya aarti at 5pm, then Hanuman poojan, chalisa and aarti at 5:30pm.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Katha at 4pm, Chopda poojan at 4:30pm, sandhya aarti at 5pm and a street food festival from 5:30pm to 8pm.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4109,17 +3936,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Diwali: Chopda poojan and street food festival</t>
+          <t>Ankoot Utsav and Hindu New Year</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4134,35 +3961,34 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Katha at 4pm, Chopda poojan at 4:30pm, sandhya aarti at 5pm and a street food festival from 5:30pm to 8pm.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Aarti 7:30am, bhajans 9am, katha and greetings 9:30am, Ankoot aarti 11am, mahaprasad 11:30am, raas 5pm, sandhya aarti 5:30pm and Ankoot prasad 6:30pm.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>shree-swaminarayan-temple-cardiff</t>
+          <t>shree-swaminarayan-temple-stanmore</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ankoot Utsav and Hindu New Year</t>
+          <t>Sharad Purnima</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://swaminarayan.wales/general-events/diwali-celebrations-2026</t>
+          <t>https://stanmoretemple.com/events/sharad-purnima-2026</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4172,10 +3998,9 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Aarti 7:30am, bhajans 9am, katha and greetings 9:30am, Ankoot aarti 11am, mahaprasad 11:30am, raas 5pm, sandhya aarti 5:30pm and Ankoot prasad 6:30pm.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Aarti, katha, kirtan and dhun from 5:30pm, then Raas Leela from 6:30pm, in the Gents &amp; Ladies Mandir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4185,22 +4010,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sharad Purnima</t>
+          <t>Kali Chaudas: Hanuman pujan</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://stanmoretemple.com/events/sharad-purnima-2026</t>
+          <t>https://stanmoretemple.com/events/diwali-2026</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -4210,10 +4035,9 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Aarti, katha, kirtan and dhun from 5:30pm, then Raas Leela from 6:30pm, in the Gents &amp; Ladies Mandir.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Hanuman Chalisa 4pm to 5:30pm, Hanuman pujan at 6pm, Hanuman Chalisa and Bajrang Baan at 7pm, and maha aarti at 8pm.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4223,17 +4047,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Kali Chaudas: Hanuman pujan</t>
+          <t>Diwali: Laxmi and Chopda pujan, and fireworks</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4248,10 +4072,9 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hanuman Chalisa 4pm to 5:30pm, Hanuman pujan at 6pm, Hanuman Chalisa and Bajrang Baan at 7pm, and maha aarti at 8pm.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Laxmi and Chopda pujan at 4:30pm (register first, then bring your own chopda and red pen), sandhya aarti at 5:30pm, and fireworks night on the event field from 6pm, with fireworks at 8pm. Free entry and parking.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4261,17 +4084,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Diwali: Laxmi and Chopda pujan, and fireworks</t>
+          <t>Nutan Varsh: Annakut darshan</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4286,35 +4109,34 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Laxmi and Chopda pujan at 4:30pm (register first, then bring your own chopda and red pen), sandhya aarti at 5:30pm, and fireworks night on the event field from 6pm, with fireworks at 8pm. Free entry and parking.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Annakut darshan from 7am with aarti every hour, and sandhya aarti with the last Annakut darshan at 6:30pm.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>shree-swaminarayan-temple-stanmore</t>
+          <t>shri-sanatan-hindu-mandir-shri-vallabh-nidhi-uk-wembley</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Nutan Varsh: Annakut darshan</t>
+          <t>Kaali Chaudash: Hanuman Chalisa</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://stanmoretemple.com/events/diwali-2026</t>
+          <t>https://svnuk.com/singlee/diwali-nutan-varsh-2026/</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4324,10 +4146,9 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Annakut darshan from 7am with aarti every hour, and sandhya aarti with the last Annakut darshan at 6:30pm.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Hanuman Chalisa from 10am to 1pm.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4337,17 +4158,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Kaali Chaudash: Hanuman Chalisa</t>
+          <t>Diwali: Chopda and Laxmi pujan</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4362,10 +4183,9 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hanuman Chalisa from 10am to 1pm.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Chopda and Laxmi pujan at 11am. Anyone can take part by donating £51 per person.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4375,17 +4195,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Diwali: Chopda and Laxmi pujan</t>
+          <t>Nutan Varsh and Annakoot darshan</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4400,48 +4220,46 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chopda and Laxmi pujan at 11am. Anyone can take part by donating £51 per person.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Annakoot darshan from 7am to 7pm, with the Nutan Varsh maha aarti at 12 noon and aartis through the day.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>shri-sanatan-hindu-mandir-shri-vallabh-nidhi-uk-wembley</t>
+          <t>shree-krishna-mandir-west-bromwich-west-bromwich</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Nutan Varsh and Annakoot darshan</t>
+          <t>Youth Club Diwali party</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://svnuk.com/singlee/diwali-nutan-varsh-2026/</t>
+          <t>https://www.shreekrishnamandir.org/</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>festival</t>
+          <t>youth</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Annakoot darshan from 7am to 7pm, with the Nutan Varsh maha aarti at 12 noon and aartis through the day.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>2pm to 5pm: arts and crafts, carrom, Diwali games, a rangoli competition, light-up sparklers and a buffet. £2 per person, under-5s free. Please let the mandir know you're coming.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4451,7 +4269,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4461,7 +4279,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Youth Club Diwali party</t>
+          <t>Diwali celebrations</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4471,40 +4289,39 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>youth</t>
+          <t>festival</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2pm to 5pm: arts and crafts, carrom, Diwali games, a rangoli competition, light-up sparklers and a buffet. £2 per person, under-5s free. Please let the mandir know you're coming.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>From 2pm: chai nasto, festive games, light a diya, fireworks and aarti. Everyone welcome, free entry.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>shree-krishna-mandir-west-bromwich-west-bromwich</t>
+          <t>the-hindu-temple-bristol</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Diwali celebrations</t>
+          <t>Karwa Chauth</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.shreekrishnamandir.org/</t>
+          <t>https://hindutemplebristol.co.uk/mandir-events/</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4514,10 +4331,9 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>From 2pm: chai nasto, festive games, light a diya, fireworks and aarti. Everyone welcome, free entry.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>4pm to 7:30pm.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4527,17 +4343,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sharad Purnima Garba</t>
+          <t>Kali Chaudas: 25 Hanuman Chalisa</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4552,10 +4363,9 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Garba in the mandir from 7:30pm.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>25 Hanuman Chalisa recitations. Time to be confirmed.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4565,17 +4375,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Karwa Chauth</t>
+          <t>Diwali: Chopda pujan</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4590,10 +4400,9 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>4pm to 7:30pm.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Chopda pujan at 8pm.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4603,13 +4412,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Kali Chaudas: 25 Hanuman Chalisa</t>
+          <t>Annakut</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4624,15 +4437,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>25 Hanuman Chalisa recitations. Time to be confirmed.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Annakut aarti at 12:30pm and evening aarti at 8pm.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>the-hindu-temple-bristol</t>
+          <t>hindu-temple-cultural-and-community-centre-nottingham</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4642,17 +4454,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Diwali: Chopda pujan</t>
+          <t>Diwali celebration</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://hindutemplebristol.co.uk/mandir-events/</t>
+          <t>https://www.hindutemple.org.uk/events-bookings/2026-diwali-8th-november-2026-6pm</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4662,35 +4474,29 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chopda pujan at 8pm.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Traditional prayers, aarti and cultural performances from 6pm.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>the-hindu-temple-bristol</t>
+          <t>bhaktivedanta-manor-iskcon-watford</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Annakut</t>
+          <t>Diwali festival</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://hindutemplebristol.co.uk/mandir-events/</t>
+          <t>https://www.krishnatemple.com/event/diwali-festival/</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4700,35 +4506,29 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Annakut aarti at 12:30pm and evening aarti at 8pm.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Darshan, drama, dances, children's activities and prasad. Free, but you need a ticket: tickets are released on Sunday 1 November at 12 noon. There are no fireworks this year.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>hindu-temple-cultural-and-community-centre-nottingham</t>
+          <t>bhaktivedanta-manor-iskcon-watford</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Diwali celebration</t>
+          <t>Annakuta and Govardhan puja</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.hindutemple.org.uk/events-bookings/2026-diwali-8th-november-2026-6pm</t>
+          <t>https://www.krishnatemple.com/event/annakuta-govardhana-puja/</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4738,31 +4538,29 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Traditional prayers, aarti and cultural performances from 6pm.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>No ticket needed.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bhaktivedanta-manor-iskcon-watford</t>
+          <t>gujarat-hindu-society-and-community-centre-preston</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>2026-10-25</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Diwali festival</t>
+          <t>Sharad Purnima</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://www.krishnatemple.com/event/diwali-festival/</t>
+          <t>https://www.ghspreston.co.uk/ghs-events-calendar/</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4770,46 +4568,43 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Darshan, drama, dances, children's activities and prasad. Free, but you need a ticket: tickets are released on Sunday 1 November at 12 noon. There are no fireworks this year.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bhaktivedanta-manor-iskcon-watford</t>
+          <t>gujarat-hindu-society-and-community-centre-preston</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Annakuta and Govardhan puja</t>
+          <t>Children's Diwali party</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://www.krishnatemple.com/event/annakuta-govardhana-puja/</t>
+          <t>https://www.ghspreston.co.uk/calendar/childrens-diwali-party-sat-31st-oct-2026/</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>festival</t>
+          <t>youth</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>No ticket needed.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Bring children at 3pm and collect them at 6pm. Volunteers are welcome to help with games.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4819,27 +4614,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sharad Purnima</t>
+          <t>Bhajan Bhojan</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://www.ghspreston.co.uk/ghs-events-calendar/</t>
+          <t>https://www.ghspreston.co.uk/calendar/bhajan-bhojan-sun-1st-nov-2026/</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>festival</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+          <t>bhajan</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Morning aarti at 9:30am, children's bhajans from 11am to 12:30pm, and bhajans and bhojan through the day until 4pm. Everyone welcome.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4849,7 +4651,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4859,12 +4661,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Children's Diwali party</t>
+          <t>Rangoli competition</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://www.ghspreston.co.uk/calendar/childrens-diwali-party-sat-31st-oct-2026/</t>
+          <t>https://www.ghspreston.co.uk/calendar/rangoli-competition-sun-1st-nov-2026/</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4874,10 +4676,9 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bring children at 3pm and collect them at 6pm. Volunteers are welcome to help with games.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>For ages 4 to 15, 3pm to 5pm. 50p per entry; collect an entry form from the office.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4892,30 +4693,29 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Bhajan Bhojan</t>
+          <t>Aarti thali decoration competition</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://www.ghspreston.co.uk/calendar/bhajan-bhojan-sun-1st-nov-2026/</t>
+          <t>https://www.ghspreston.co.uk/calendar/aarti-thali-decoration-competition-sun-1st-nov-2026/</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>bhajan</t>
+          <t>community</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Morning aarti at 9:30am, children's bhajans from 11am to 12:30pm, and bhajans and bhojan through the day until 4pm. Everyone welcome.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Decorate a 12-inch thali at home and bring it to the mandir by 2:30pm; judging at 4pm.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4925,35 +4725,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Rangoli competition</t>
+          <t>Diwali and fireworks</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://www.ghspreston.co.uk/calendar/rangoli-competition-sun-1st-nov-2026/</t>
+          <t>https://www.ghspreston.co.uk/ghs-events-calendar/</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>youth</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>For ages 4 to 15, 3pm to 5pm. 50p per entry; collect an entry form from the office.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>festival</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4963,56 +4752,49 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Aarti thali decoration competition</t>
+          <t>New Year and Annakut</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://www.ghspreston.co.uk/calendar/aarti-thali-decoration-competition-sun-1st-nov-2026/</t>
+          <t>https://www.ghspreston.co.uk/ghs-events-calendar/</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>community</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Decorate a 12-inch thali at home and bring it to the mandir by 2:30pm; judging at 4pm.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>festival</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>gujarat-hindu-society-and-community-centre-preston</t>
+          <t>shree-hindu-temple-and-community-centre-leicester</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Diwali and fireworks</t>
+          <t>Sharad Purnima</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://www.ghspreston.co.uk/ghs-events-calendar/</t>
+          <t>https://www.shreehindutemple.net/</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -5020,29 +4802,31 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>From 7:30pm until late. Tickets £5 from the mandir.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>gujarat-hindu-society-and-community-centre-preston</t>
+          <t>shree-hindu-temple-and-community-centre-leicester</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>2026-11-08</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>New Year and Annakut</t>
+          <t>Diwali: Chopda pujan</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://www.ghspreston.co.uk/ghs-events-calendar/</t>
+          <t>https://www.shreehindutemple.net/hinduism/festivals-list-2026/</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5050,8 +4834,11 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Chopda pujan in the mandir. Times to be confirmed.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5061,22 +4848,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sharad Purnima</t>
+          <t>New Year and Annakut darshan</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://www.shreehindutemple.net/</t>
+          <t>https://www.shreehindutemple.net/hinduism/festivals-list-2026/</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5086,31 +4868,29 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>From 7:30pm until late. Tickets £5 from the mandir.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Vikram Samvat 2083. Times to be confirmed.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>shree-hindu-temple-and-community-centre-leicester</t>
+          <t>shree-jalaram-mandir-greenford</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>2026-10-25</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Diwali: Chopda pujan</t>
+          <t>Sharad Purnima</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://www.shreehindutemple.net/hinduism/festivals-list-2026/</t>
+          <t>https://jalarammandir.co.uk/events/</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5118,33 +4898,26 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Chopda pujan in the mandir. Times to be confirmed.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>shree-hindu-temple-and-community-centre-leicester</t>
+          <t>shree-jalaram-mandir-greenford</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>2026-11-08</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>New Year and Annakut darshan</t>
+          <t>Diwali and Chopda pujan</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://www.shreehindutemple.net/hinduism/festivals-list-2026/</t>
+          <t>https://jalarammandir.co.uk/events/</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5152,12 +4925,6 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Vikram Samvat 2083. Times to be confirmed.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5167,13 +4934,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>2026-11-09</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sharad Purnima</t>
+          <t>Nutan Varsh and Annakut darshan</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5186,8 +4952,6 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5197,13 +4961,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>2026-11-16</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Diwali and Chopda pujan</t>
+          <t>227th Jalaram Jayanti celebration</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5216,29 +4979,31 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>shree-jalaram-mandir-greenford</t>
+          <t>shree-kutch-satsang-swaminarayan-temple-kenton</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Nutan Varsh and Annakut darshan</t>
+          <t>Sharad Poonam</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://jalarammandir.co.uk/events/</t>
+          <t>https://sksst.org/</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5246,29 +5011,31 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Aarti, thaal, chesta and katha from 4:30pm to 6:15pm, raas from 6:15pm to 7pm, then the Sharad Poonam aarti with dudhpaak, puri and marcha prasad for all.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>shree-jalaram-mandir-greenford</t>
+          <t>shree-kutch-satsang-swaminarayan-temple-kenton</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>2026-11-07</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>227th Jalaram Jayanti celebration</t>
+          <t>Kali Chaudash: Hanuman pujan</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://jalarammandir.co.uk/events/</t>
+          <t>https://sksst.org/</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5276,8 +5043,11 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Timings to be confirmed.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5287,17 +5057,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sharad Poonam</t>
+          <t>Diwali: Laxmi and Chopda pujan</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5312,10 +5077,9 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Aarti, thaal, chesta and katha from 4:30pm to 6:15pm, raas from 6:15pm to 7pm, then the Sharad Poonam aarti with dudhpaak, puri and marcha prasad for all.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Timings to be confirmed.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5325,13 +5089,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>2026-11-09</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Kali Chaudash: Hanuman pujan</t>
+          <t>Annakutotsav and Nutan Varsh</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5346,31 +5109,34 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Timings to be confirmed.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Govardhan pujan and the new year. Timings to be confirmed.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>shree-kutch-satsang-swaminarayan-temple-kenton</t>
+          <t>shree-swaminarayan-mandir-oldham</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Diwali: Laxmi and Chopda pujan</t>
+          <t>Sharad Poonam</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://sksst.org/</t>
+          <t>https://oldhammandir.faith/</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5380,31 +5146,34 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Timings to be confirmed.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Raas followed by dudhpak prasad, from 6:30pm.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>shree-kutch-satsang-swaminarayan-temple-kenton</t>
+          <t>shri-venkateswara-balaji-temple-tividale</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>2026-11-08</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Annakutotsav and Nutan Varsh</t>
+          <t>Festival of Lights: peace walk and fireworks</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://sksst.org/</t>
+          <t>https://www.venkateswara.org.uk/religious-events/festival-of-lights-to-celebrate-deepawali-2026</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5414,73 +5183,71 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Govardhan pujan and the new year. Timings to be confirmed.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>A peace walk from the Balaji Temple at 5:30pm and a fireworks display at 7pm.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>shree-swaminarayan-mandir-oldham</t>
+          <t>shri-venkateswara-balaji-temple-tividale</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ramayan: the divine Diwali story</t>
+          <t>Deepawali Samuha Dhanalakshmi pooja</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://oldhammandir.faith/</t>
+          <t>https://www.venkateswara.org.uk/religious-events/deepawali-samuha-dhanalakshmi-pooja-2026</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>youth</t>
+          <t>festival</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>The Bal Mandal (children's group) present the Ramayan on stage, from 7pm, followed by light nasto.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Group Dhanalakshmi pooja at 6:30pm.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>shree-swaminarayan-mandir-oldham</t>
+          <t>london-sri-mahalakshmi-temple-east-ham</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sharad Poonam</t>
+          <t>Deepavali: Kedara Gowri pooja</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://oldhammandir.faith/</t>
+          <t>https://www.srimahalakshmitemple.net/UpcomingEvents.cshtml</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5490,15 +5257,14 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Raas followed by dudhpak prasad, from 6:30pm.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Kedara Gowri pooja at 3pm and 6pm.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>shri-venkateswara-balaji-temple-tividale</t>
+          <t>sri-raja-rajeswary-amman-temple-stoneleigh</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5506,19 +5272,14 @@
           <t>2026-11-08</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Festival of Lights: peace walk and fireworks</t>
+          <t>Deepavali and Kethara Gowri Viratham</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://www.venkateswara.org.uk/religious-events/festival-of-lights-to-celebrate-deepawali-2026</t>
+          <t>https://srirajarajeswary.org.uk/event/</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5526,37 +5287,31 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>A peace walk from the Balaji Temple at 5:30pm and a fireworks display at 7pm.</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>shri-venkateswara-balaji-temple-tividale</t>
+          <t>iskcon-london-radha-krishna-temple-soho</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Deepawali Samuha Dhanalakshmi pooja</t>
+          <t>Sharad Purnima</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://www.venkateswara.org.uk/religious-events/deepawali-samuha-dhanalakshmi-pooja-2026</t>
+          <t>https://iskcon.london/</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5566,15 +5321,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Group Dhanalakshmi pooja at 6:30pm.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>6pm to 9:30pm.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>london-sri-mahalakshmi-temple-east-ham</t>
+          <t>iskcon-leicester</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5582,19 +5336,14 @@
           <t>2026-11-08</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Deepavali: Kedara Gowri pooja</t>
+          <t>Dipavali</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://www.srimahalakshmitemple.net/UpcomingEvents.cshtml</t>
+          <t>https://iskconleicester.org/</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5602,33 +5351,26 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Kedara Gowri pooja at 3pm and 6pm.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>sri-raja-rajeswary-amman-temple-stoneleigh</t>
+          <t>iskcon-leicester</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>2026-11-09</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Deepavali and Kethara Gowri Viratham</t>
+          <t>Govardhan puja</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://srirajarajeswary.org.uk/event/</t>
+          <t>https://iskconleicester.org/</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5636,144 +5378,43 @@
           <t>festival</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>iskcon-london-radha-krishna-temple-soho</t>
+          <t>wellingborough-hindu-mandir-wdha</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sharad Purnima</t>
+          <t>Wellingborough Festival of Lights</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://iskcon.london/</t>
+          <t>https://wdha.co.uk/calendar/wellingborough-festival-of-lights-2026/</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>festival</t>
+          <t>community</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>6pm to 9:30pm.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>iskcon-leicester</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2026-11-08</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Dipavali</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>https://iskconleicester.org/</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>festival</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>iskcon-leicester</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2026-11-09</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Govardhan puja</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>https://iskconleicester.org/</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>festival</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>wellingborough-hindu-mandir-wdha</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Wellingborough Festival of Lights</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>https://wdha.co.uk/calendar/wellingborough-festival-of-lights-2026/</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>community</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
           <t>The town's Festival of Lights returns, 11am to 9pm, with workshops, performances and more across Wellingborough. See the WDHA page for where things are.</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6906,7 +6547,6 @@
           <t>Leicester</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -6924,7 +6564,6 @@
           <t>Luton</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -6942,7 +6581,6 @@
           <t>Peterborough</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -6960,7 +6598,6 @@
           <t>Newport</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -6978,7 +6615,6 @@
           <t>Exeter</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -6996,7 +6632,6 @@
           <t>Gloucester</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7014,7 +6649,6 @@
           <t>Romford</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7032,7 +6666,6 @@
           <t>Leicester</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7050,7 +6683,6 @@
           <t>Middlesbrough</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7068,7 +6700,6 @@
           <t>Milton Keynes</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7086,7 +6717,6 @@
           <t>Sheffield</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7104,7 +6734,6 @@
           <t>Huddersfield</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7122,7 +6751,6 @@
           <t>Belfast</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7140,7 +6768,6 @@
           <t>Manchester</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7158,7 +6785,6 @@
           <t>Newcastle</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7176,7 +6802,6 @@
           <t>Swansea</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7194,7 +6819,6 @@
           <t>Harrow</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7212,7 +6836,6 @@
           <t>Ipswich</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7230,7 +6853,6 @@
           <t>Leicester</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7248,7 +6870,6 @@
           <t>Harrow</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7266,7 +6887,6 @@
           <t>Gillingham</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7284,7 +6904,6 @@
           <t>Oxford</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7302,7 +6921,6 @@
           <t>Cardiff</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7320,7 +6938,6 @@
           <t>Leicester</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7338,7 +6955,6 @@
           <t>Leicester</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7356,7 +6972,6 @@
           <t>Plumstead</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7374,7 +6989,6 @@
           <t>Walsall</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7392,7 +7006,6 @@
           <t>Bolton</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7410,7 +7023,6 @@
           <t>Kingsbury</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7428,7 +7040,6 @@
           <t>South Harrow</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7446,7 +7057,6 @@
           <t>Wolverhampton</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7464,7 +7074,6 @@
           <t>Harrow</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7482,7 +7091,6 @@
           <t>Harrow</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7500,7 +7108,6 @@
           <t>Tooting</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7518,7 +7125,6 @@
           <t>Gravesend</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7536,7 +7142,6 @@
           <t>Leeds</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
           <t>No website on Toran</t>
@@ -7554,7 +7159,6 @@
           <t>Southall</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
           <t>No website on Toran</t>
